--- a/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="B1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,6 +1234,21 @@
           <t>Y/N</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -1256,6 +1271,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -1278,6 +1304,17 @@
           <t>No</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -1300,6 +1337,17 @@
           <t>TBC</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1311,6 +1359,17 @@
         <is>
           <t>Support meeting</t>
         </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Responsible AI section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Responsible AI section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr"/>

--- a/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,16 @@
       <b val="1"/>
       <color rgb="00002060"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -172,58 +183,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +612,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="24" customWidth="1" min="11" max="11"/>
@@ -650,7 +663,7 @@
 • Provide commentary on progress towards each target (Column M or N)
 • Provide supporting documentation if required (Column O), including links to images
 • Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
-• Your end-2025 responses (where a related target existed) can be viewed by clicking the [+] icon above Columns H–K
+• Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
 • Due: Friday 15 January 2027 (TBC). Questions: Sustainability Strategy team (sustainability-strategy@unimelb.edu.au – TBC)</t>
@@ -728,7 +741,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1413,4 +1426,75 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2025 target status assessment and reporting (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Your SR25 responses – Chief Information Officer Group (CIOG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>← Back to request</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>No end-2025 request was issued to this area (new to Sustainability 2030 reporting).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIOG - end-2026 sustainability reporting request.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1223,217 +1223,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>End 2026 target status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data owner confirms</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Request status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Please select from dropdown</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not sent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Partially – see comments</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chased</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Support meeting</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1497,4 +1286,215 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>End 2026 target status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data owner confirms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Request status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Please select from dropdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially – see comments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chased</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support meeting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>